--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743050</v>
+        <v>122743054</v>
       </c>
       <c r="B2" t="n">
-        <v>78729</v>
+        <v>78796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599448</v>
+        <v>599455</v>
       </c>
       <c r="R2" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743053</v>
+        <v>122743052</v>
       </c>
       <c r="B3" t="n">
-        <v>79770</v>
+        <v>78831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599462</v>
+        <v>599446</v>
       </c>
       <c r="R3" t="n">
-        <v>6873503</v>
+        <v>6873501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743051</v>
+        <v>122743045</v>
       </c>
       <c r="B4" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599447</v>
+        <v>599455</v>
       </c>
       <c r="R4" t="n">
-        <v>6873502</v>
+        <v>6873499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743044</v>
+        <v>122743053</v>
       </c>
       <c r="B5" t="n">
-        <v>78729</v>
+        <v>79872</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599449</v>
+        <v>599462</v>
       </c>
       <c r="R5" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743049</v>
+        <v>122743051</v>
       </c>
       <c r="B6" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599438</v>
+        <v>599447</v>
       </c>
       <c r="R6" t="n">
-        <v>6873491</v>
+        <v>6873502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1189,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743039</v>
+        <v>122743040</v>
       </c>
       <c r="B7" t="n">
-        <v>79741</v>
+        <v>78831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599443</v>
+        <v>599450</v>
       </c>
       <c r="R7" t="n">
-        <v>6873491</v>
+        <v>6873489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743038</v>
+        <v>122743047</v>
       </c>
       <c r="B8" t="n">
-        <v>90802</v>
+        <v>78831</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1343,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599417</v>
+        <v>599448</v>
       </c>
       <c r="R8" t="n">
-        <v>6873431</v>
+        <v>6873499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743042</v>
+        <v>122743046</v>
       </c>
       <c r="B9" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599450</v>
+        <v>599452</v>
       </c>
       <c r="R9" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743054</v>
+        <v>122743039</v>
       </c>
       <c r="B10" t="n">
-        <v>78694</v>
+        <v>79843</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,34 +1569,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599455</v>
+        <v>599443</v>
       </c>
       <c r="R10" t="n">
-        <v>6873503</v>
+        <v>6873491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743045</v>
+        <v>122743038</v>
       </c>
       <c r="B11" t="n">
-        <v>78729</v>
+        <v>90905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,38 +1671,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599455</v>
+        <v>599417</v>
       </c>
       <c r="R11" t="n">
-        <v>6873499</v>
+        <v>6873431</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,11 +1735,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743046</v>
+        <v>122743050</v>
       </c>
       <c r="B12" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,14 +1801,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599452</v>
+        <v>599448</v>
       </c>
       <c r="R12" t="n">
-        <v>6873497</v>
+        <v>6873496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743040</v>
+        <v>122743044</v>
       </c>
       <c r="B13" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R13" t="n">
-        <v>6873489</v>
+        <v>6873496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743047</v>
+        <v>122743043</v>
       </c>
       <c r="B14" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,14 +2023,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R14" t="n">
-        <v>6873499</v>
+        <v>6873505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,7 +2101,7 @@
         <v>122743048</v>
       </c>
       <c r="B15" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743043</v>
+        <v>122743041</v>
       </c>
       <c r="B16" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,14 +2245,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>599450</v>
       </c>
       <c r="R16" t="n">
-        <v>6873505</v>
+        <v>6873497</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743052</v>
+        <v>122743049</v>
       </c>
       <c r="B17" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599446</v>
+        <v>599438</v>
       </c>
       <c r="R17" t="n">
-        <v>6873501</v>
+        <v>6873491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743041</v>
+        <v>122743042</v>
       </c>
       <c r="B18" t="n">
-        <v>78729</v>
+        <v>78831</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>599450</v>
       </c>
       <c r="R18" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743046</v>
+        <v>122743039</v>
       </c>
       <c r="B9" t="n">
-        <v>78831</v>
+        <v>79843</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,38 +1454,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599452</v>
+        <v>599443</v>
       </c>
       <c r="R9" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743039</v>
+        <v>122743046</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>78831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,38 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599443</v>
+        <v>599452</v>
       </c>
       <c r="R10" t="n">
-        <v>6873491</v>
+        <v>6873497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,6 +1624,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743054</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>78800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743052</v>
+        <v>122743042</v>
       </c>
       <c r="B3" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599446</v>
+        <v>599450</v>
       </c>
       <c r="R3" t="n">
-        <v>6873501</v>
+        <v>6873503</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743045</v>
+        <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R4" t="n">
-        <v>6873499</v>
+        <v>6873489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743053</v>
+        <v>122743051</v>
       </c>
       <c r="B5" t="n">
-        <v>79872</v>
+        <v>78835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599462</v>
+        <v>599447</v>
       </c>
       <c r="R5" t="n">
-        <v>6873503</v>
+        <v>6873502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743051</v>
+        <v>122743043</v>
       </c>
       <c r="B6" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,14 +1150,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599447</v>
+        <v>599450</v>
       </c>
       <c r="R6" t="n">
-        <v>6873502</v>
+        <v>6873505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743040</v>
+        <v>122743046</v>
       </c>
       <c r="B7" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,14 +1261,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599450</v>
+        <v>599452</v>
       </c>
       <c r="R7" t="n">
-        <v>6873489</v>
+        <v>6873497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,7 +1339,7 @@
         <v>122743047</v>
       </c>
       <c r="B8" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743039</v>
+        <v>122743049</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>78835</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,35 +1459,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599443</v>
+        <v>599438</v>
       </c>
       <c r="R9" t="n">
         <v>6873491</v>
@@ -1518,6 +1523,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743046</v>
+        <v>122743050</v>
       </c>
       <c r="B10" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,14 +1594,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599452</v>
+        <v>599448</v>
       </c>
       <c r="R10" t="n">
-        <v>6873497</v>
+        <v>6873496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1638,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1672,7 @@
         <v>122743038</v>
       </c>
       <c r="B11" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743050</v>
+        <v>122743044</v>
       </c>
       <c r="B12" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,11 +1811,11 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599448</v>
+        <v>599449</v>
       </c>
       <c r="R12" t="n">
         <v>6873496</v>
@@ -1845,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743044</v>
+        <v>122743039</v>
       </c>
       <c r="B13" t="n">
-        <v>78831</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,38 +1898,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599449</v>
+        <v>599443</v>
       </c>
       <c r="R13" t="n">
-        <v>6873496</v>
+        <v>6873491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,11 +1962,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743043</v>
+        <v>122743053</v>
       </c>
       <c r="B14" t="n">
-        <v>78831</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,38 +2004,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599450</v>
+        <v>599462</v>
       </c>
       <c r="R14" t="n">
-        <v>6873505</v>
+        <v>6873503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,11 +2068,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,7 +2101,7 @@
         <v>122743048</v>
       </c>
       <c r="B15" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>122743041</v>
       </c>
       <c r="B16" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743049</v>
+        <v>122743052</v>
       </c>
       <c r="B17" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599438</v>
+        <v>599446</v>
       </c>
       <c r="R17" t="n">
-        <v>6873491</v>
+        <v>6873501</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743042</v>
+        <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>78831</v>
+        <v>78835</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R18" t="n">
-        <v>6873503</v>
+        <v>6873499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743054</v>
+        <v>122743041</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>78835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R2" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743042</v>
+        <v>122743049</v>
       </c>
       <c r="B3" t="n">
         <v>78835</v>
@@ -817,14 +822,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599450</v>
+        <v>599438</v>
       </c>
       <c r="R3" t="n">
-        <v>6873503</v>
+        <v>6873491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743040</v>
+        <v>122743051</v>
       </c>
       <c r="B4" t="n">
         <v>78835</v>
@@ -928,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599450</v>
+        <v>599447</v>
       </c>
       <c r="R4" t="n">
-        <v>6873489</v>
+        <v>6873502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743051</v>
+        <v>122743039</v>
       </c>
       <c r="B5" t="n">
-        <v>78835</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,38 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599447</v>
+        <v>599443</v>
       </c>
       <c r="R5" t="n">
-        <v>6873502</v>
+        <v>6873491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743043</v>
+        <v>122743038</v>
       </c>
       <c r="B6" t="n">
-        <v>78835</v>
+        <v>90909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,38 +1126,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599450</v>
+        <v>599417</v>
       </c>
       <c r="R6" t="n">
-        <v>6873505</v>
+        <v>6873431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1190,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743046</v>
+        <v>122743043</v>
       </c>
       <c r="B7" t="n">
         <v>78835</v>
@@ -1261,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599452</v>
+        <v>599450</v>
       </c>
       <c r="R7" t="n">
-        <v>6873497</v>
+        <v>6873505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743049</v>
+        <v>122743053</v>
       </c>
       <c r="B9" t="n">
-        <v>78835</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599438</v>
+        <v>599462</v>
       </c>
       <c r="R9" t="n">
-        <v>6873491</v>
+        <v>6873503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743038</v>
+        <v>122743042</v>
       </c>
       <c r="B11" t="n">
-        <v>90909</v>
+        <v>78835</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,38 +1671,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599417</v>
+        <v>599450</v>
       </c>
       <c r="R11" t="n">
-        <v>6873431</v>
+        <v>6873503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,6 +1735,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743044</v>
+        <v>122743045</v>
       </c>
       <c r="B12" t="n">
         <v>78835</v>
@@ -1815,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599449</v>
+        <v>599455</v>
       </c>
       <c r="R12" t="n">
-        <v>6873496</v>
+        <v>6873499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743039</v>
+        <v>122743054</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,34 +1897,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599443</v>
+        <v>599455</v>
       </c>
       <c r="R13" t="n">
-        <v>6873491</v>
+        <v>6873503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743053</v>
+        <v>122743046</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>78835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,25 +1999,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599462</v>
+        <v>599452</v>
       </c>
       <c r="R14" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,6 +2063,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743048</v>
+        <v>122743040</v>
       </c>
       <c r="B15" t="n">
         <v>78835</v>
@@ -2134,14 +2134,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599449</v>
+        <v>599450</v>
       </c>
       <c r="R15" t="n">
-        <v>6873494</v>
+        <v>6873489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743041</v>
+        <v>122743048</v>
       </c>
       <c r="B16" t="n">
         <v>78835</v>
@@ -2245,14 +2245,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R16" t="n">
-        <v>6873497</v>
+        <v>6873494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743052</v>
+        <v>122743044</v>
       </c>
       <c r="B17" t="n">
         <v>78835</v>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599446</v>
+        <v>599449</v>
       </c>
       <c r="R17" t="n">
-        <v>6873501</v>
+        <v>6873496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743045</v>
+        <v>122743052</v>
       </c>
       <c r="B18" t="n">
         <v>78835</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599455</v>
+        <v>599446</v>
       </c>
       <c r="R18" t="n">
-        <v>6873499</v>
+        <v>6873501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743041</v>
+        <v>122743049</v>
       </c>
       <c r="B2" t="n">
         <v>78835</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599450</v>
+        <v>599438</v>
       </c>
       <c r="R2" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743049</v>
+        <v>122743044</v>
       </c>
       <c r="B3" t="n">
         <v>78835</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599438</v>
+        <v>599449</v>
       </c>
       <c r="R3" t="n">
-        <v>6873491</v>
+        <v>6873496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743051</v>
+        <v>122743038</v>
       </c>
       <c r="B4" t="n">
-        <v>78835</v>
+        <v>90909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599447</v>
+        <v>599417</v>
       </c>
       <c r="R4" t="n">
-        <v>6873502</v>
+        <v>6873431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743039</v>
+        <v>122743050</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1015,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599443</v>
+        <v>599448</v>
       </c>
       <c r="R5" t="n">
-        <v>6873491</v>
+        <v>6873496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743038</v>
+        <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>90909</v>
+        <v>78835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,38 +1126,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599417</v>
+        <v>599449</v>
       </c>
       <c r="R6" t="n">
-        <v>6873431</v>
+        <v>6873494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743043</v>
+        <v>122743041</v>
       </c>
       <c r="B7" t="n">
         <v>78835</v>
@@ -1256,14 +1261,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>599450</v>
       </c>
       <c r="R7" t="n">
-        <v>6873505</v>
+        <v>6873497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743047</v>
+        <v>122743053</v>
       </c>
       <c r="B8" t="n">
-        <v>78835</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599448</v>
+        <v>599462</v>
       </c>
       <c r="R8" t="n">
-        <v>6873499</v>
+        <v>6873503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743053</v>
+        <v>122743051</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>78835</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599462</v>
+        <v>599447</v>
       </c>
       <c r="R9" t="n">
-        <v>6873503</v>
+        <v>6873502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,6 +1518,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743050</v>
+        <v>122743054</v>
       </c>
       <c r="B10" t="n">
-        <v>78835</v>
+        <v>78800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1565,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599448</v>
+        <v>599455</v>
       </c>
       <c r="R10" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,11 +1629,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743042</v>
+        <v>122743047</v>
       </c>
       <c r="B11" t="n">
         <v>78835</v>
@@ -1695,14 +1695,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599450</v>
+        <v>599448</v>
       </c>
       <c r="R11" t="n">
-        <v>6873503</v>
+        <v>6873499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743045</v>
+        <v>122743042</v>
       </c>
       <c r="B12" t="n">
         <v>78835</v>
@@ -1806,14 +1806,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R12" t="n">
-        <v>6873499</v>
+        <v>6873503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743054</v>
+        <v>122743039</v>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,34 +1897,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599455</v>
+        <v>599443</v>
       </c>
       <c r="R13" t="n">
-        <v>6873503</v>
+        <v>6873491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743040</v>
+        <v>122743045</v>
       </c>
       <c r="B15" t="n">
         <v>78835</v>
@@ -2134,14 +2134,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R15" t="n">
-        <v>6873489</v>
+        <v>6873499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743048</v>
+        <v>122743043</v>
       </c>
       <c r="B16" t="n">
         <v>78835</v>
@@ -2245,14 +2245,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599449</v>
+        <v>599450</v>
       </c>
       <c r="R16" t="n">
-        <v>6873494</v>
+        <v>6873505</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743044</v>
+        <v>122743052</v>
       </c>
       <c r="B17" t="n">
         <v>78835</v>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599449</v>
+        <v>599446</v>
       </c>
       <c r="R17" t="n">
-        <v>6873496</v>
+        <v>6873501</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743052</v>
+        <v>122743040</v>
       </c>
       <c r="B18" t="n">
         <v>78835</v>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599446</v>
+        <v>599450</v>
       </c>
       <c r="R18" t="n">
-        <v>6873501</v>
+        <v>6873489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743049</v>
+        <v>122743045</v>
       </c>
       <c r="B2" t="n">
         <v>78835</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599438</v>
+        <v>599455</v>
       </c>
       <c r="R2" t="n">
-        <v>6873491</v>
+        <v>6873499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743044</v>
+        <v>122743052</v>
       </c>
       <c r="B3" t="n">
         <v>78835</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599449</v>
+        <v>599446</v>
       </c>
       <c r="R3" t="n">
-        <v>6873496</v>
+        <v>6873501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743038</v>
+        <v>122743039</v>
       </c>
       <c r="B4" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599417</v>
+        <v>599443</v>
       </c>
       <c r="R4" t="n">
-        <v>6873431</v>
+        <v>6873491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743050</v>
+        <v>122743046</v>
       </c>
       <c r="B5" t="n">
         <v>78835</v>
@@ -1039,14 +1039,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599448</v>
+        <v>599452</v>
       </c>
       <c r="R5" t="n">
-        <v>6873496</v>
+        <v>6873497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743048</v>
+        <v>122743053</v>
       </c>
       <c r="B6" t="n">
-        <v>78835</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599449</v>
+        <v>599462</v>
       </c>
       <c r="R6" t="n">
-        <v>6873494</v>
+        <v>6873503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1190,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743041</v>
+        <v>122743042</v>
       </c>
       <c r="B7" t="n">
         <v>78835</v>
@@ -1261,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>599450</v>
       </c>
       <c r="R7" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743053</v>
+        <v>122743043</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>78835</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,38 +1343,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599462</v>
+        <v>599450</v>
       </c>
       <c r="R8" t="n">
-        <v>6873503</v>
+        <v>6873505</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743051</v>
+        <v>122743041</v>
       </c>
       <c r="B9" t="n">
         <v>78835</v>
@@ -1478,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599447</v>
+        <v>599450</v>
       </c>
       <c r="R9" t="n">
-        <v>6873502</v>
+        <v>6873497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743054</v>
+        <v>122743040</v>
       </c>
       <c r="B10" t="n">
-        <v>78800</v>
+        <v>78835</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,38 +1565,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R10" t="n">
-        <v>6873503</v>
+        <v>6873489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743047</v>
+        <v>122743044</v>
       </c>
       <c r="B11" t="n">
         <v>78835</v>
@@ -1699,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599448</v>
+        <v>599449</v>
       </c>
       <c r="R11" t="n">
-        <v>6873499</v>
+        <v>6873496</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743042</v>
+        <v>122743054</v>
       </c>
       <c r="B12" t="n">
-        <v>78835</v>
+        <v>78800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,35 +1787,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R12" t="n">
         <v>6873503</v>
@@ -1846,11 +1851,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743039</v>
+        <v>122743051</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78835</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,38 +1893,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599443</v>
+        <v>599447</v>
       </c>
       <c r="R13" t="n">
-        <v>6873491</v>
+        <v>6873502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,6 +1957,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743046</v>
+        <v>122743038</v>
       </c>
       <c r="B14" t="n">
-        <v>78835</v>
+        <v>90909</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,38 +2004,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599452</v>
+        <v>599417</v>
       </c>
       <c r="R14" t="n">
-        <v>6873497</v>
+        <v>6873431</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,11 +2068,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743045</v>
+        <v>122743049</v>
       </c>
       <c r="B15" t="n">
         <v>78835</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599455</v>
+        <v>599438</v>
       </c>
       <c r="R15" t="n">
-        <v>6873499</v>
+        <v>6873491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743043</v>
+        <v>122743048</v>
       </c>
       <c r="B16" t="n">
         <v>78835</v>
@@ -2245,14 +2245,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R16" t="n">
-        <v>6873505</v>
+        <v>6873494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743052</v>
+        <v>122743047</v>
       </c>
       <c r="B17" t="n">
         <v>78835</v>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599446</v>
+        <v>599448</v>
       </c>
       <c r="R17" t="n">
-        <v>6873501</v>
+        <v>6873499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743040</v>
+        <v>122743050</v>
       </c>
       <c r="B18" t="n">
         <v>78835</v>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599450</v>
+        <v>599448</v>
       </c>
       <c r="R18" t="n">
-        <v>6873489</v>
+        <v>6873496</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743052</v>
+        <v>122743039</v>
       </c>
       <c r="B3" t="n">
-        <v>78835</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599446</v>
+        <v>599443</v>
       </c>
       <c r="R3" t="n">
-        <v>6873501</v>
+        <v>6873491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743039</v>
+        <v>122743052</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599443</v>
+        <v>599446</v>
       </c>
       <c r="R4" t="n">
-        <v>6873491</v>
+        <v>6873501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743045</v>
+        <v>122743043</v>
       </c>
       <c r="B2" t="n">
         <v>78835</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R2" t="n">
-        <v>6873499</v>
+        <v>6873505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743039</v>
+        <v>122743038</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599443</v>
+        <v>599417</v>
       </c>
       <c r="R3" t="n">
-        <v>6873491</v>
+        <v>6873431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743052</v>
+        <v>122743054</v>
       </c>
       <c r="B4" t="n">
-        <v>78835</v>
+        <v>78800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599446</v>
+        <v>599455</v>
       </c>
       <c r="R4" t="n">
-        <v>6873501</v>
+        <v>6873503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743046</v>
+        <v>122743047</v>
       </c>
       <c r="B5" t="n">
         <v>78835</v>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599452</v>
+        <v>599448</v>
       </c>
       <c r="R5" t="n">
-        <v>6873497</v>
+        <v>6873499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743053</v>
+        <v>122743041</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>78835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,38 +1121,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599462</v>
+        <v>599450</v>
       </c>
       <c r="R6" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,6 +1185,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743042</v>
+        <v>122743044</v>
       </c>
       <c r="B7" t="n">
         <v>78835</v>
@@ -1256,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R7" t="n">
-        <v>6873503</v>
+        <v>6873496</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743043</v>
+        <v>122743048</v>
       </c>
       <c r="B8" t="n">
         <v>78835</v>
@@ -1367,14 +1367,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R8" t="n">
-        <v>6873505</v>
+        <v>6873494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743041</v>
+        <v>122743052</v>
       </c>
       <c r="B9" t="n">
         <v>78835</v>
@@ -1478,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599450</v>
+        <v>599446</v>
       </c>
       <c r="R9" t="n">
-        <v>6873497</v>
+        <v>6873501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743040</v>
+        <v>122743042</v>
       </c>
       <c r="B10" t="n">
         <v>78835</v>
@@ -1589,14 +1589,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>599450</v>
       </c>
       <c r="R10" t="n">
-        <v>6873489</v>
+        <v>6873503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743044</v>
+        <v>122743039</v>
       </c>
       <c r="B11" t="n">
-        <v>78835</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,38 +1676,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599449</v>
+        <v>599443</v>
       </c>
       <c r="R11" t="n">
-        <v>6873496</v>
+        <v>6873491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,11 +1740,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743054</v>
+        <v>122743046</v>
       </c>
       <c r="B12" t="n">
-        <v>78800</v>
+        <v>78835</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,38 +1782,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599455</v>
+        <v>599452</v>
       </c>
       <c r="R12" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,6 +1846,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,7 +1881,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743051</v>
+        <v>122743050</v>
       </c>
       <c r="B13" t="n">
         <v>78835</v>
@@ -1917,14 +1917,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599447</v>
+        <v>599448</v>
       </c>
       <c r="R13" t="n">
-        <v>6873502</v>
+        <v>6873496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743038</v>
+        <v>122743053</v>
       </c>
       <c r="B14" t="n">
-        <v>90909</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,34 +2008,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599417</v>
+        <v>599462</v>
       </c>
       <c r="R14" t="n">
-        <v>6873431</v>
+        <v>6873503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743049</v>
+        <v>122743040</v>
       </c>
       <c r="B15" t="n">
         <v>78835</v>
@@ -2134,14 +2134,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599438</v>
+        <v>599450</v>
       </c>
       <c r="R15" t="n">
-        <v>6873491</v>
+        <v>6873489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743048</v>
+        <v>122743049</v>
       </c>
       <c r="B16" t="n">
         <v>78835</v>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599449</v>
+        <v>599438</v>
       </c>
       <c r="R16" t="n">
-        <v>6873494</v>
+        <v>6873491</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743047</v>
+        <v>122743045</v>
       </c>
       <c r="B17" t="n">
         <v>78835</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599448</v>
+        <v>599455</v>
       </c>
       <c r="R17" t="n">
         <v>6873499</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743050</v>
+        <v>122743051</v>
       </c>
       <c r="B18" t="n">
         <v>78835</v>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599448</v>
+        <v>599447</v>
       </c>
       <c r="R18" t="n">
-        <v>6873496</v>
+        <v>6873502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743046</v>
+        <v>122743053</v>
       </c>
       <c r="B12" t="n">
-        <v>78835</v>
+        <v>79876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599452</v>
+        <v>599462</v>
       </c>
       <c r="R12" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,11 +1846,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743050</v>
+        <v>122743046</v>
       </c>
       <c r="B13" t="n">
         <v>78835</v>
@@ -1917,14 +1912,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599448</v>
+        <v>599452</v>
       </c>
       <c r="R13" t="n">
-        <v>6873496</v>
+        <v>6873497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743053</v>
+        <v>122743050</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>78835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,38 +1999,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599462</v>
+        <v>599448</v>
       </c>
       <c r="R14" t="n">
-        <v>6873503</v>
+        <v>6873496</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,6 +2063,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743043</v>
+        <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599450</v>
+        <v>599446</v>
       </c>
       <c r="R2" t="n">
-        <v>6873505</v>
+        <v>6873501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743038</v>
+        <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>78833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599417</v>
+        <v>599450</v>
       </c>
       <c r="R3" t="n">
-        <v>6873431</v>
+        <v>6873497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743054</v>
+        <v>122743045</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>78833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>599455</v>
       </c>
       <c r="R4" t="n">
-        <v>6873503</v>
+        <v>6873499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743047</v>
+        <v>122743048</v>
       </c>
       <c r="B5" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599448</v>
+        <v>599449</v>
       </c>
       <c r="R5" t="n">
-        <v>6873499</v>
+        <v>6873494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743041</v>
+        <v>122743050</v>
       </c>
       <c r="B6" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,14 +1155,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599450</v>
+        <v>599448</v>
       </c>
       <c r="R6" t="n">
-        <v>6873497</v>
+        <v>6873496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1199,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743044</v>
+        <v>122743038</v>
       </c>
       <c r="B7" t="n">
-        <v>78835</v>
+        <v>90917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,38 +1242,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599449</v>
+        <v>599417</v>
       </c>
       <c r="R7" t="n">
-        <v>6873496</v>
+        <v>6873431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743048</v>
+        <v>122743040</v>
       </c>
       <c r="B8" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,14 +1372,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599449</v>
+        <v>599450</v>
       </c>
       <c r="R8" t="n">
-        <v>6873494</v>
+        <v>6873489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743052</v>
+        <v>122743047</v>
       </c>
       <c r="B9" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599446</v>
+        <v>599448</v>
       </c>
       <c r="R9" t="n">
-        <v>6873501</v>
+        <v>6873499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743042</v>
+        <v>122743039</v>
       </c>
       <c r="B10" t="n">
-        <v>78835</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,38 +1570,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599450</v>
+        <v>599443</v>
       </c>
       <c r="R10" t="n">
-        <v>6873503</v>
+        <v>6873491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,11 +1634,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743039</v>
+        <v>122743046</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,38 +1676,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599443</v>
+        <v>599452</v>
       </c>
       <c r="R11" t="n">
-        <v>6873491</v>
+        <v>6873497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,6 +1740,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743053</v>
+        <v>122743054</v>
       </c>
       <c r="B12" t="n">
-        <v>79876</v>
+        <v>78798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,35 +1787,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599462</v>
+        <v>599455</v>
       </c>
       <c r="R12" t="n">
         <v>6873503</v>
@@ -1876,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743046</v>
+        <v>122743049</v>
       </c>
       <c r="B13" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599452</v>
+        <v>599438</v>
       </c>
       <c r="R13" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1961,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743050</v>
+        <v>122743042</v>
       </c>
       <c r="B14" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,14 +2028,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R14" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2072,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743040</v>
+        <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,14 +2139,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599450</v>
+        <v>599447</v>
       </c>
       <c r="R15" t="n">
-        <v>6873489</v>
+        <v>6873502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743049</v>
+        <v>122743044</v>
       </c>
       <c r="B16" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599438</v>
+        <v>599449</v>
       </c>
       <c r="R16" t="n">
-        <v>6873491</v>
+        <v>6873496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2294,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743045</v>
+        <v>122743053</v>
       </c>
       <c r="B17" t="n">
-        <v>78835</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,25 +2337,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599455</v>
+        <v>599462</v>
       </c>
       <c r="R17" t="n">
-        <v>6873499</v>
+        <v>6873503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,11 +2401,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743051</v>
+        <v>122743043</v>
       </c>
       <c r="B18" t="n">
-        <v>78835</v>
+        <v>78833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599447</v>
+        <v>599450</v>
       </c>
       <c r="R18" t="n">
-        <v>6873502</v>
+        <v>6873505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743052</v>
+        <v>122743040</v>
       </c>
       <c r="B2" t="n">
         <v>78833</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599446</v>
+        <v>599450</v>
       </c>
       <c r="R2" t="n">
-        <v>6873501</v>
+        <v>6873489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743041</v>
+        <v>122743039</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599450</v>
+        <v>599443</v>
       </c>
       <c r="R3" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743045</v>
+        <v>122743038</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599455</v>
+        <v>599417</v>
       </c>
       <c r="R4" t="n">
-        <v>6873499</v>
+        <v>6873431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743048</v>
+        <v>122743052</v>
       </c>
       <c r="B5" t="n">
         <v>78833</v>
@@ -1048,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599449</v>
+        <v>599446</v>
       </c>
       <c r="R5" t="n">
-        <v>6873494</v>
+        <v>6873501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743050</v>
+        <v>122743044</v>
       </c>
       <c r="B6" t="n">
         <v>78833</v>
@@ -1155,11 +1145,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599448</v>
+        <v>599449</v>
       </c>
       <c r="R6" t="n">
         <v>6873496</v>
@@ -1199,7 +1189,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743038</v>
+        <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>90917</v>
+        <v>78833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,38 +1232,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599417</v>
+        <v>599448</v>
       </c>
       <c r="R7" t="n">
-        <v>6873431</v>
+        <v>6873496</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743040</v>
+        <v>122743046</v>
       </c>
       <c r="B8" t="n">
         <v>78833</v>
@@ -1372,14 +1367,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599450</v>
+        <v>599452</v>
       </c>
       <c r="R8" t="n">
-        <v>6873489</v>
+        <v>6873497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743047</v>
+        <v>122743042</v>
       </c>
       <c r="B9" t="n">
         <v>78833</v>
@@ -1483,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R9" t="n">
-        <v>6873499</v>
+        <v>6873503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743039</v>
+        <v>122743053</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,38 +1565,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599443</v>
+        <v>599462</v>
       </c>
       <c r="R10" t="n">
-        <v>6873491</v>
+        <v>6873503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743046</v>
+        <v>122743049</v>
       </c>
       <c r="B11" t="n">
         <v>78833</v>
@@ -1704,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599452</v>
+        <v>599438</v>
       </c>
       <c r="R11" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743054</v>
+        <v>122743048</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>78833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,38 +1782,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599455</v>
+        <v>599449</v>
       </c>
       <c r="R12" t="n">
-        <v>6873503</v>
+        <v>6873494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,6 +1846,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743049</v>
+        <v>122743054</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>78798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,38 +1893,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599438</v>
+        <v>599455</v>
       </c>
       <c r="R13" t="n">
-        <v>6873491</v>
+        <v>6873503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,11 +1957,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,7 +1987,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743042</v>
+        <v>122743045</v>
       </c>
       <c r="B14" t="n">
         <v>78833</v>
@@ -2028,14 +2023,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R14" t="n">
-        <v>6873503</v>
+        <v>6873499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743051</v>
+        <v>122743043</v>
       </c>
       <c r="B15" t="n">
         <v>78833</v>
@@ -2139,14 +2134,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599447</v>
+        <v>599450</v>
       </c>
       <c r="R15" t="n">
-        <v>6873502</v>
+        <v>6873505</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743044</v>
+        <v>122743047</v>
       </c>
       <c r="B16" t="n">
         <v>78833</v>
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599449</v>
+        <v>599448</v>
       </c>
       <c r="R16" t="n">
-        <v>6873496</v>
+        <v>6873499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743053</v>
+        <v>122743041</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>78833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,38 +2332,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599462</v>
+        <v>599450</v>
       </c>
       <c r="R17" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,6 +2396,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743043</v>
+        <v>122743051</v>
       </c>
       <c r="B18" t="n">
         <v>78833</v>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599450</v>
+        <v>599447</v>
       </c>
       <c r="R18" t="n">
-        <v>6873505</v>
+        <v>6873502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743040</v>
+        <v>122743045</v>
       </c>
       <c r="B2" t="n">
         <v>78833</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R2" t="n">
-        <v>6873489</v>
+        <v>6873499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743039</v>
+        <v>122743046</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599443</v>
+        <v>599452</v>
       </c>
       <c r="R3" t="n">
-        <v>6873491</v>
+        <v>6873497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743038</v>
+        <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>78833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599417</v>
+        <v>599450</v>
       </c>
       <c r="R4" t="n">
-        <v>6873431</v>
+        <v>6873489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743052</v>
+        <v>122743038</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>90917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599446</v>
+        <v>599417</v>
       </c>
       <c r="R5" t="n">
-        <v>6873501</v>
+        <v>6873431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743044</v>
+        <v>122743053</v>
       </c>
       <c r="B6" t="n">
-        <v>78833</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599449</v>
+        <v>599462</v>
       </c>
       <c r="R6" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,11 +1190,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743050</v>
+        <v>122743042</v>
       </c>
       <c r="B7" t="n">
         <v>78833</v>
@@ -1256,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R7" t="n">
-        <v>6873496</v>
+        <v>6873503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743046</v>
+        <v>122743049</v>
       </c>
       <c r="B8" t="n">
         <v>78833</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599452</v>
+        <v>599438</v>
       </c>
       <c r="R8" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743042</v>
+        <v>122743050</v>
       </c>
       <c r="B9" t="n">
         <v>78833</v>
@@ -1478,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599450</v>
+        <v>599448</v>
       </c>
       <c r="R9" t="n">
-        <v>6873503</v>
+        <v>6873496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743053</v>
+        <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>78833</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,25 +1565,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599462</v>
+        <v>599448</v>
       </c>
       <c r="R10" t="n">
-        <v>6873503</v>
+        <v>6873499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743049</v>
+        <v>122743039</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,35 +1676,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599438</v>
+        <v>599443</v>
       </c>
       <c r="R11" t="n">
         <v>6873491</v>
@@ -1735,11 +1740,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743048</v>
+        <v>122743043</v>
       </c>
       <c r="B12" t="n">
         <v>78833</v>
@@ -1806,14 +1806,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599449</v>
+        <v>599450</v>
       </c>
       <c r="R12" t="n">
-        <v>6873494</v>
+        <v>6873505</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743054</v>
+        <v>122743052</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>78833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,38 +1893,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599455</v>
+        <v>599446</v>
       </c>
       <c r="R13" t="n">
-        <v>6873503</v>
+        <v>6873501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,6 +1957,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,7 +1992,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743045</v>
+        <v>122743044</v>
       </c>
       <c r="B14" t="n">
         <v>78833</v>
@@ -2027,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599455</v>
+        <v>599449</v>
       </c>
       <c r="R14" t="n">
-        <v>6873499</v>
+        <v>6873496</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2072,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2103,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743043</v>
+        <v>122743041</v>
       </c>
       <c r="B15" t="n">
         <v>78833</v>
@@ -2134,14 +2139,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>599450</v>
       </c>
       <c r="R15" t="n">
-        <v>6873505</v>
+        <v>6873497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2214,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743047</v>
+        <v>122743048</v>
       </c>
       <c r="B16" t="n">
         <v>78833</v>
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599448</v>
+        <v>599449</v>
       </c>
       <c r="R16" t="n">
-        <v>6873499</v>
+        <v>6873494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2294,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743041</v>
+        <v>122743054</v>
       </c>
       <c r="B17" t="n">
-        <v>78833</v>
+        <v>78798</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,38 +2337,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R17" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,11 +2401,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743045</v>
+        <v>122743051</v>
       </c>
       <c r="B2" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599455</v>
+        <v>599447</v>
       </c>
       <c r="R2" t="n">
-        <v>6873499</v>
+        <v>6873502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743046</v>
+        <v>122743054</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599452</v>
+        <v>599455</v>
       </c>
       <c r="R3" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743040</v>
+        <v>122743039</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599450</v>
+        <v>599443</v>
       </c>
       <c r="R4" t="n">
-        <v>6873489</v>
+        <v>6873491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743038</v>
+        <v>122743040</v>
       </c>
       <c r="B5" t="n">
-        <v>90917</v>
+        <v>78836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1010,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599417</v>
+        <v>599450</v>
       </c>
       <c r="R5" t="n">
-        <v>6873431</v>
+        <v>6873489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743053</v>
+        <v>122743052</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>78836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599462</v>
+        <v>599446</v>
       </c>
       <c r="R6" t="n">
-        <v>6873503</v>
+        <v>6873501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,6 +1185,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743042</v>
+        <v>122743053</v>
       </c>
       <c r="B7" t="n">
-        <v>78833</v>
+        <v>79879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,35 +1232,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599450</v>
+        <v>599462</v>
       </c>
       <c r="R7" t="n">
         <v>6873503</v>
@@ -1296,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743049</v>
+        <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>90920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1338,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>637</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Långsjön N, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599438</v>
+        <v>599417</v>
       </c>
       <c r="R8" t="n">
-        <v>6873491</v>
+        <v>6873431</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,11 +1402,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743050</v>
+        <v>122743043</v>
       </c>
       <c r="B9" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,14 +1468,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R9" t="n">
-        <v>6873496</v>
+        <v>6873505</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1512,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743047</v>
+        <v>122743045</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,7 +1583,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599448</v>
+        <v>599455</v>
       </c>
       <c r="R10" t="n">
         <v>6873499</v>
@@ -1633,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743039</v>
+        <v>122743049</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,35 +1666,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599443</v>
+        <v>599438</v>
       </c>
       <c r="R11" t="n">
         <v>6873491</v>
@@ -1740,6 +1730,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743043</v>
+        <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,7 +1808,7 @@
         <v>599450</v>
       </c>
       <c r="R12" t="n">
-        <v>6873505</v>
+        <v>6873503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743052</v>
+        <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599446</v>
+        <v>599452</v>
       </c>
       <c r="R13" t="n">
-        <v>6873501</v>
+        <v>6873497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743044</v>
+        <v>122743050</v>
       </c>
       <c r="B14" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,11 +2023,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599449</v>
+        <v>599448</v>
       </c>
       <c r="R14" t="n">
         <v>6873496</v>
@@ -2072,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743041</v>
+        <v>122743044</v>
       </c>
       <c r="B15" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,14 +2134,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R15" t="n">
-        <v>6873497</v>
+        <v>6873496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743048</v>
+        <v>122743047</v>
       </c>
       <c r="B16" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599449</v>
+        <v>599448</v>
       </c>
       <c r="R16" t="n">
-        <v>6873494</v>
+        <v>6873499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743054</v>
+        <v>122743048</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,38 +2332,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599455</v>
+        <v>599449</v>
       </c>
       <c r="R17" t="n">
-        <v>6873503</v>
+        <v>6873494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,6 +2396,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743051</v>
+        <v>122743041</v>
       </c>
       <c r="B18" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599447</v>
+        <v>599450</v>
       </c>
       <c r="R18" t="n">
-        <v>6873502</v>
+        <v>6873497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743051</v>
+        <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599447</v>
+        <v>599446</v>
       </c>
       <c r="R2" t="n">
-        <v>6873502</v>
+        <v>6873501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743054</v>
+        <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599455</v>
+        <v>599450</v>
       </c>
       <c r="R3" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743039</v>
+        <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>78838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599443</v>
+        <v>599450</v>
       </c>
       <c r="R4" t="n">
-        <v>6873491</v>
+        <v>6873489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743040</v>
+        <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>78836</v>
+        <v>78803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R5" t="n">
-        <v>6873489</v>
+        <v>6873503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743052</v>
+        <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599446</v>
+        <v>599449</v>
       </c>
       <c r="R6" t="n">
-        <v>6873501</v>
+        <v>6873494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743053</v>
+        <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>78838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,38 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lidberget NÖ, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599462</v>
+        <v>599448</v>
       </c>
       <c r="R7" t="n">
-        <v>6873503</v>
+        <v>6873496</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1301,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1339,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743043</v>
+        <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,14 +1478,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599450</v>
+        <v>599449</v>
       </c>
       <c r="R9" t="n">
-        <v>6873505</v>
+        <v>6873496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743045</v>
+        <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,7 +1593,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599455</v>
+        <v>599448</v>
       </c>
       <c r="R10" t="n">
         <v>6873499</v>
@@ -1623,7 +1633,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743049</v>
+        <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>78836</v>
+        <v>79881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1676,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599438</v>
+        <v>599462</v>
       </c>
       <c r="R11" t="n">
-        <v>6873491</v>
+        <v>6873503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,11 +1740,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1773,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,7 +1884,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743050</v>
+        <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,14 +2028,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599448</v>
+        <v>599438</v>
       </c>
       <c r="R14" t="n">
-        <v>6873496</v>
+        <v>6873491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2072,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743044</v>
+        <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599449</v>
+        <v>599447</v>
       </c>
       <c r="R15" t="n">
-        <v>6873496</v>
+        <v>6873502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743047</v>
+        <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,14 +2250,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599448</v>
+        <v>599450</v>
       </c>
       <c r="R16" t="n">
-        <v>6873499</v>
+        <v>6873505</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2294,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743048</v>
+        <v>122743045</v>
       </c>
       <c r="B17" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599449</v>
+        <v>599455</v>
       </c>
       <c r="R17" t="n">
-        <v>6873494</v>
+        <v>6873499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743041</v>
+        <v>122743039</v>
       </c>
       <c r="B18" t="n">
-        <v>78836</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2443,25 +2448,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599450</v>
+        <v>599443</v>
       </c>
       <c r="R18" t="n">
-        <v>6873497</v>
+        <v>6873491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,11 +2512,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -2325,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743045</v>
+        <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,38 +2337,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599455</v>
+        <v>599443</v>
       </c>
       <c r="R17" t="n">
-        <v>6873499</v>
+        <v>6873491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,11 +2401,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743039</v>
+        <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>78838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,38 +2443,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599443</v>
+        <v>599455</v>
       </c>
       <c r="R18" t="n">
-        <v>6873491</v>
+        <v>6873499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,6 +2507,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743052</v>
       </c>
       <c r="B2" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743041</v>
       </c>
       <c r="B3" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122743040</v>
       </c>
       <c r="B4" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122743054</v>
       </c>
       <c r="B5" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>122743048</v>
       </c>
       <c r="B6" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>122743050</v>
       </c>
       <c r="B7" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>122743038</v>
       </c>
       <c r="B8" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>122743044</v>
       </c>
       <c r="B9" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>122743047</v>
       </c>
       <c r="B10" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122743053</v>
       </c>
       <c r="B11" t="n">
-        <v>80462</v>
+        <v>80463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>122743042</v>
       </c>
       <c r="B12" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>122743046</v>
       </c>
       <c r="B13" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>122743049</v>
       </c>
       <c r="B14" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>122743051</v>
       </c>
       <c r="B15" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>122743043</v>
       </c>
       <c r="B16" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122743039</v>
       </c>
       <c r="B17" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>122743045</v>
       </c>
       <c r="B18" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743052</v>
+        <v>122743054</v>
       </c>
       <c r="B2" t="n">
-        <v>79399</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Renskinns- V, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599446</v>
+        <v>599455</v>
       </c>
       <c r="R2" t="n">
-        <v>6873501</v>
+        <v>6873503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743041</v>
+        <v>113678294</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,16 +805,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599450</v>
+        <v>599424</v>
       </c>
       <c r="R3" t="n">
-        <v>6873497</v>
+        <v>6873546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,17 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,8 +858,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -887,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743040</v>
+        <v>113678295</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +915,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599450</v>
+        <v>599422</v>
       </c>
       <c r="R4" t="n">
-        <v>6873489</v>
+        <v>6873544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,17 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,8 +968,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -993,45 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743054</v>
+        <v>113678296</v>
       </c>
       <c r="B5" t="n">
-        <v>79364</v>
+        <v>79440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- V, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599455</v>
+        <v>599422</v>
       </c>
       <c r="R5" t="n">
-        <v>6873503</v>
+        <v>6873550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,12 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,8 +1078,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1094,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743048</v>
+        <v>113678297</v>
       </c>
       <c r="B6" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,16 +1135,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599449</v>
+        <v>599414</v>
       </c>
       <c r="R6" t="n">
-        <v>6873494</v>
+        <v>6873551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,17 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,8 +1188,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1200,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743050</v>
+        <v>113678298</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,16 +1245,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lidberget NÖ, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599448</v>
+        <v>599416</v>
       </c>
       <c r="R7" t="n">
-        <v>6873496</v>
+        <v>6873550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,17 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran 11 cm. Ca 15 bålar.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,8 +1298,14 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,45 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743038</v>
+        <v>113678299</v>
       </c>
       <c r="B8" t="n">
-        <v>91879</v>
+        <v>79440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjön N, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599417</v>
+        <v>599415</v>
       </c>
       <c r="R8" t="n">
-        <v>6873431</v>
+        <v>6873548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,12 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,8 +1408,14 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1407,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743044</v>
+        <v>113678300</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,16 +1465,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599449</v>
+        <v>599422</v>
       </c>
       <c r="R9" t="n">
-        <v>6873496</v>
+        <v>6873555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,17 +1504,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,8 +1518,14 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1513,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743047</v>
+        <v>113678301</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,16 +1575,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599448</v>
+        <v>599419</v>
       </c>
       <c r="R10" t="n">
-        <v>6873499</v>
+        <v>6873553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,17 +1614,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,8 +1628,14 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1619,45 +1656,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743053</v>
+        <v>122743040</v>
       </c>
       <c r="B11" t="n">
-        <v>80466</v>
+        <v>79440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599462</v>
+        <v>599450</v>
       </c>
       <c r="R11" t="n">
-        <v>6873503</v>
+        <v>6873489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1727,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran 5 cm i brh. Jämte tall 48 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743042</v>
+        <v>122743041</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,14 +1793,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Lappberget N, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>599450</v>
       </c>
       <c r="R12" t="n">
-        <v>6873503</v>
+        <v>6873497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1837,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
+          <t>På gran ca 18 cm i brh. Minst 1 bål. I kanten av hänsyn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743046</v>
+        <v>122743042</v>
       </c>
       <c r="B13" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,14 +1899,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599452</v>
+        <v>599450</v>
       </c>
       <c r="R13" t="n">
-        <v>6873497</v>
+        <v>6873503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
+          <t>Gran ca 17 cm i brh. Ca 5 bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743049</v>
+        <v>122743043</v>
       </c>
       <c r="B14" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,14 +2005,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Hls</t>
+          <t>Kullbergstjärnarna Ö, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599438</v>
+        <v>599450</v>
       </c>
       <c r="R14" t="n">
-        <v>6873491</v>
+        <v>6873505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2049,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743051</v>
+        <v>122743044</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599447</v>
+        <v>599449</v>
       </c>
       <c r="R15" t="n">
-        <v>6873502</v>
+        <v>6873496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2155,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+          <t>På gran ca 26 i brh. Rikligt med bålar. Minst ett 30 tal. Även långt upp i trädet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743043</v>
+        <v>122743045</v>
       </c>
       <c r="B16" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,14 +2217,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullbergstjärnarna Ö, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599450</v>
+        <v>599455</v>
       </c>
       <c r="R16" t="n">
-        <v>6873505</v>
+        <v>6873499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2261,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran 9 cm i brh. Ca 7 bålar.</t>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,45 +2292,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122743039</v>
+        <v>122743046</v>
       </c>
       <c r="B17" t="n">
-        <v>80437</v>
+        <v>79440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lappberget N, Hls</t>
+          <t>Renskinns- NV, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599443</v>
+        <v>599452</v>
       </c>
       <c r="R17" t="n">
-        <v>6873491</v>
+        <v>6873497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,6 +2363,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gran ca 7 cm. Toppen av. 2 bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122743045</v>
+        <v>122743047</v>
       </c>
       <c r="B18" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,7 +2433,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599455</v>
+        <v>599448</v>
       </c>
       <c r="R18" t="n">
         <v>6873499</v>
@@ -2426,7 +2473,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 4 cm i brh. 1 bål.</t>
+          <t>Gran 20 cm i brh. Rikligt med bålar. Minst ett 30-tal. Men även rikligt med skägglav.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2450,6 +2497,945 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122743048</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>637</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>599449</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6873494</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran ca 4 cm i brh. 1 bål.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122743049</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>637</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>599438</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6873491</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122743050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>637</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lidberget NÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599448</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6873496</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gran 11 cm. Ca 15 bålar.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122743051</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>637</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599447</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6873502</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran 7 cm i brh. Ca 10 bålar. Står jämte granen med plus 100 bålar.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122743052</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>637</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>599446</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6873501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113679867</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nybodvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>599367</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6873357</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122743038</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långsjön N, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>599417</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6873431</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122743039</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lappberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>599443</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6873491</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122743053</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>599462</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6873503</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 382-2024 artfynd.xlsx
+++ b/artfynd/A 382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743054</t>
         </is>
       </c>
     </row>
@@ -883,6 +893,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678294</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678295</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678297</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678298</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678299</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678300</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678301</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743040</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743041</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743044</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2289,6 +2364,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743045</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2395,6 +2475,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743046</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743047</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2607,6 +2697,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743048</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2713,6 +2808,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743049</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2819,6 +2919,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2925,6 +3030,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743051</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743052</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3137,6 +3252,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679867</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3238,6 +3358,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743038</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3339,6 +3464,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743039</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3440,8 +3570,41 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743053</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>